--- a/tables/table-6-final-finetuning-results.xlsx
+++ b/tables/table-6-final-finetuning-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{5D509599-3738-478A-B4D6-ED3A47B41BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDB2745-42E0-484F-B0D9-9CA856FCA5E7}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{5D509599-3738-478A-B4D6-ED3A47B41BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C0BBA1D-1291-4A3C-A367-7BDDD837E5CB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E598B19D-FC76-46E8-9ADE-382599A1DB4E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Architecture</t>
   </si>
@@ -36,12 +36,6 @@
     <t>Unfrozen Layers</t>
   </si>
   <si>
-    <t>Total Confused Pairs</t>
-  </si>
-  <si>
-    <t>Training Time</t>
-  </si>
-  <si>
     <t>EfficientNet-B0</t>
   </si>
   <si>
@@ -51,9 +45,6 @@
     <t>features[5,6,7] &amp; classifier</t>
   </si>
   <si>
-    <t>3 h 22 min 9 s</t>
-  </si>
-  <si>
     <t>MobileNetV2</t>
   </si>
   <si>
@@ -63,9 +54,6 @@
     <t>features[16,17,18] &amp; classifier</t>
   </si>
   <si>
-    <t>2 h 35 min 43 s</t>
-  </si>
-  <si>
     <t>ViT-B/16</t>
   </si>
   <si>
@@ -75,9 +63,6 @@
     <t>encoder.layers[8,9,10,11] &amp; heads</t>
   </si>
   <si>
-    <t>22 h 35 min 14 s</t>
-  </si>
-  <si>
     <t>CoaT-Lite Medium</t>
   </si>
   <si>
@@ -87,16 +72,25 @@
     <t>serial_blocks4[4,5,6,7] &amp; norm4 &amp; head</t>
   </si>
   <si>
-    <t>14 h 43 min 5 s</t>
-  </si>
-  <si>
     <t>Table 7: Final Fine-Tuning Results</t>
   </si>
   <si>
-    <t>Test Accuracy (%)</t>
-  </si>
-  <si>
-    <t>Trainable (%)</t>
+    <t>Trainable Parameters (%)</t>
+  </si>
+  <si>
+    <t>Total Parameters</t>
+  </si>
+  <si>
+    <t>4.1M</t>
+  </si>
+  <si>
+    <t>2.3M</t>
+  </si>
+  <si>
+    <t>85.8M</t>
+  </si>
+  <si>
+    <t>44.1M</t>
   </si>
 </sst>
 </file>
@@ -182,7 +176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,9 +187,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -205,32 +196,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -547,147 +517,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46064B7-74C8-4852-A972-17228D454F2A}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="1" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-    </row>
-    <row r="2" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2">
-        <v>82.3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="14">
-        <v>99.6</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
-        <v>55.5</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="15">
-        <v>100</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="2">
-        <v>33.1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="15">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="E6" s="5">
         <v>28.7</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="16">
-        <v>99.6</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
